--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_31.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_31.xlsx
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ExamPass?</t>
+          <t>Interesting</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ExamGrade</t>
+          <t>HoursSleep</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>1.04318408113294</v>
+        <v>-1.189605966757044</v>
       </c>
       <c r="C2">
-        <v>0.4807037053006069</v>
+        <v>-0.4723139346008213</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>2.06013831559267</v>
+        <v>-0.8359327672706069</v>
       </c>
       <c r="C3">
-        <v>2.179942259460392</v>
+        <v>-0.2473214374749717</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.741343512291262</v>
+        <v>-1.484996982611551</v>
       </c>
       <c r="C4">
-        <v>1.042582448197455</v>
+        <v>0.6176858192599123</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.7777221120828369</v>
+        <v>-1.667786289324582</v>
       </c>
       <c r="C5">
-        <v>-1.568425464102177</v>
+        <v>-1.721384136644877</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.543025692360034</v>
+        <v>0.01299500330153277</v>
       </c>
       <c r="C6">
-        <v>1.122475992805224</v>
+        <v>0.3816211173974589</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-1.352965028915221</v>
+        <v>1.601222425919538</v>
       </c>
       <c r="C7">
-        <v>-0.8341132794117929</v>
+        <v>1.8659671306473</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.6706024969376055</v>
+        <v>1.087346067349316</v>
       </c>
       <c r="C8">
-        <v>1.163696954225106</v>
+        <v>1.342891265787846</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>1.472161411807426</v>
+        <v>-0.6664306543518831</v>
       </c>
       <c r="C9">
-        <v>0.07651563604942879</v>
+        <v>0.7250130831268846</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.9693102712491597</v>
+        <v>0.9912197558350877</v>
       </c>
       <c r="C10">
-        <v>-1.283158167634862</v>
+        <v>0.8765214110201682</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.4726856950828448</v>
+        <v>0.4293230524116593</v>
       </c>
       <c r="C11">
-        <v>-0.7374883313719549</v>
+        <v>0.5230071485141998</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.8915523489361684</v>
+        <v>0.2986811848672912</v>
       </c>
       <c r="C12">
-        <v>-0.4564626043151132</v>
+        <v>-0.4522221184816983</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>1.246009067571812</v>
+        <v>1.651740510376312</v>
       </c>
       <c r="C13">
-        <v>0.8256996601448886</v>
+        <v>-1.68264804497618</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.5972544684126425</v>
+        <v>0.4100667794337772</v>
       </c>
       <c r="C14">
-        <v>-0.3217657057284496</v>
+        <v>0.5628490873063442</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.7161196587532613</v>
+        <v>1.288772803529196</v>
       </c>
       <c r="C15">
-        <v>1.750169111793493</v>
+        <v>-0.3600284556807326</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-1.585102962924795</v>
+        <v>0.6743572636187398</v>
       </c>
       <c r="C16">
-        <v>-1.4175725894894</v>
+        <v>1.884513703692998</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-0.2084094153478184</v>
+        <v>-0.7043230969638705</v>
       </c>
       <c r="C17">
-        <v>-0.09167423262329935</v>
+        <v>-0.258439708293866</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>1.454092823501085</v>
+        <v>0.08477449944068395</v>
       </c>
       <c r="C18">
-        <v>1.060976012725807</v>
+        <v>-0.09607640063272352</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.9045594125072682</v>
+        <v>1.385489478384398</v>
       </c>
       <c r="C19">
-        <v>0.5874459891664139</v>
+        <v>0.1687363288993604</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.5414898875455403</v>
+        <v>-0.3693143919810101</v>
       </c>
       <c r="C20">
-        <v>0.1381061203084537</v>
+        <v>0.24754812991754</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.3800430914006077</v>
+        <v>1.348354715318287</v>
       </c>
       <c r="C21">
-        <v>1.329148864498796</v>
+        <v>0.3696527676220452</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.2055880330038119</v>
+        <v>0.2692918374738253</v>
       </c>
       <c r="C22">
-        <v>-1.570638742559481</v>
+        <v>1.805204473712387</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-1.008022973702641</v>
+        <v>1.304478164446398</v>
       </c>
       <c r="C23">
-        <v>0.3541906429623883</v>
+        <v>-0.07946640542793104</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.2004490162747731</v>
+        <v>-1.653358181153924</v>
       </c>
       <c r="C24">
-        <v>-0.08634001094713324</v>
+        <v>0.7251724288404756</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>1.114133866428365</v>
+        <v>2.276021546835722</v>
       </c>
       <c r="C25">
-        <v>-0.4829549845512405</v>
+        <v>1.782933607569834</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.1205810677228289</v>
+        <v>0.1664679556749801</v>
       </c>
       <c r="C26">
-        <v>0.1431086002529749</v>
+        <v>-0.9879880840687963</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.6519948042288782</v>
+        <v>1.832742357805397</v>
       </c>
       <c r="C27">
-        <v>-0.3367872038381783</v>
+        <v>0.2418021438197422</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>1.469482395592662</v>
+        <v>0.6273173850249987</v>
       </c>
       <c r="C28">
-        <v>-0.5312267729754716</v>
+        <v>-1.329529840866317</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.5539112000732204</v>
+        <v>1.349599235269083</v>
       </c>
       <c r="C29">
-        <v>-0.2597774758844625</v>
+        <v>0.4363528073260212</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.2917749027905618</v>
+        <v>0.4586250817093089</v>
       </c>
       <c r="C30">
-        <v>-0.6613244713122191</v>
+        <v>-1.127598399744893</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>1.732335889776067</v>
+        <v>0.7319343388646264</v>
       </c>
       <c r="C31">
-        <v>1.944796372333218</v>
+        <v>-0.1959635486695893</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.01882912967944713</v>
+        <v>-1.074510403211811</v>
       </c>
       <c r="C32">
-        <v>-1.596387463991923</v>
+        <v>0.02013063423827882</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.5972476666576919</v>
+        <v>0.2420340255864204</v>
       </c>
       <c r="C33">
-        <v>0.3684486687764749</v>
+        <v>-0.4475949953237151</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.9721096282352422</v>
+        <v>-1.167667170507769</v>
       </c>
       <c r="C34">
-        <v>0.5864028929267451</v>
+        <v>-1.229011329011831</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>1.187208236999391</v>
+        <v>1.292034390207261</v>
       </c>
       <c r="C35">
-        <v>1.017315733286613</v>
+        <v>1.229236435705481</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.8179482847219632</v>
+        <v>-1.050597890622337</v>
       </c>
       <c r="C36">
-        <v>-0.3371878183283685</v>
+        <v>0.4296845152574552</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.1633615428279566</v>
+        <v>0.1373791583066489</v>
       </c>
       <c r="C37">
-        <v>-0.2622293818170766</v>
+        <v>-1.685339652531299</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.9708000985095763</v>
+        <v>1.732570961477964</v>
       </c>
       <c r="C38">
-        <v>0.8025786772139869</v>
+        <v>1.221739570817916</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.3368668033021412</v>
+        <v>0.8860744005001422</v>
       </c>
       <c r="C39">
-        <v>0.6120921264532921</v>
+        <v>2.56659583228249</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>1.65795541786462</v>
+        <v>-0.4188921377244115</v>
       </c>
       <c r="C40">
-        <v>-0.5029645499199458</v>
+        <v>2.144235916149346</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.5614802885912</v>
+        <v>0.3160603254658647</v>
       </c>
       <c r="C41">
-        <v>-1.242748059901787</v>
+        <v>1.895209378270364</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.6243631588970547</v>
+        <v>1.737837449477895</v>
       </c>
       <c r="C42">
-        <v>-0.8718354992345576</v>
+        <v>-0.194331224171069</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.2920539717324113</v>
+        <v>-0.1668960100416148</v>
       </c>
       <c r="C43">
-        <v>0.1995875170388376</v>
+        <v>0.7666016746701376</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.7874342768113466</v>
+        <v>-0.9954059711343388</v>
       </c>
       <c r="C44">
-        <v>0.2776529223618981</v>
+        <v>-0.7185440149485234</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.545394690046633</v>
+        <v>-1.528401352883373</v>
       </c>
       <c r="C45">
-        <v>-0.04245806216564108</v>
+        <v>-1.373843309175006</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.5140960882061316</v>
+        <v>0.4173085915275547</v>
       </c>
       <c r="C46">
-        <v>0.366744271887256</v>
+        <v>0.3951030995630438</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.2449300992639741</v>
+        <v>1.184868214156414</v>
       </c>
       <c r="C47">
-        <v>-0.3712183729867631</v>
+        <v>-0.1070901232998068</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.09382606088995669</v>
+        <v>-2.02839564388245</v>
       </c>
       <c r="C48">
-        <v>0.1436153600820493</v>
+        <v>-0.1629603960750782</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.6565079298125919</v>
+        <v>2.134219482399303</v>
       </c>
       <c r="C49">
-        <v>-0.03998082166674971</v>
+        <v>1.494091303868818</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.677192395676264</v>
+        <v>0.7630398937982398</v>
       </c>
       <c r="C50">
-        <v>0.4526227115679277</v>
+        <v>1.190183983789123</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>2.73197875268013</v>
+        <v>-0.3392545186889575</v>
       </c>
       <c r="C51">
-        <v>0.2368914100735823</v>
+        <v>-0.7134411298479982</v>
       </c>
     </row>
     <row r="52">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>-0.6030974101107919</v>
+        <v>-1.1231920497261</v>
       </c>
       <c r="C52">
-        <v>-1.268442258475209</v>
+        <v>0.2099006546597763</v>
       </c>
     </row>
     <row r="53">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>-2.208795564354327</v>
+        <v>0.5242866408075927</v>
       </c>
       <c r="C53">
-        <v>-0.6420390846015036</v>
+        <v>0.4779188535316732</v>
       </c>
     </row>
     <row r="54">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>-0.8034568172396246</v>
+        <v>-1.53492646718162</v>
       </c>
       <c r="C54">
-        <v>0.100514232136377</v>
+        <v>-0.6664955222781133</v>
       </c>
     </row>
     <row r="55">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>1.049843116884598</v>
+        <v>0.3590977830330933</v>
       </c>
       <c r="C55">
-        <v>1.883305969718775</v>
+        <v>0.3717566292097304</v>
       </c>
     </row>
     <row r="56">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>-1.36202280867712</v>
+        <v>-0.5392089634711725</v>
       </c>
       <c r="C56">
-        <v>-1.05573597077075</v>
+        <v>-1.017206799226562</v>
       </c>
     </row>
     <row r="57">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.3956619137875194</v>
+        <v>-0.6295042512872443</v>
       </c>
       <c r="C57">
-        <v>1.563919494550363</v>
+        <v>1.145035330052498</v>
       </c>
     </row>
     <row r="58">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>-0.6032800039928847</v>
+        <v>-1.470080862815147</v>
       </c>
       <c r="C58">
-        <v>0.1489931486585681</v>
+        <v>-0.6354058461074714</v>
       </c>
     </row>
     <row r="59">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>1.510525907108116</v>
+        <v>-0.9696231103307886</v>
       </c>
       <c r="C59">
-        <v>-0.290549485386823</v>
+        <v>-1.246769917168999</v>
       </c>
     </row>
     <row r="60">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>0.624708364060344</v>
+        <v>-0.5382720383958846</v>
       </c>
       <c r="C60">
-        <v>2.298468603861413</v>
+        <v>-0.3805440023468949</v>
       </c>
     </row>
     <row r="61">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>0.4379905065089758</v>
+        <v>-1.050626456424757</v>
       </c>
       <c r="C61">
-        <v>1.290355779355067</v>
+        <v>0.3478578398583376</v>
       </c>
     </row>
     <row r="62">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>2.99073352789483</v>
+        <v>1.398868591495572</v>
       </c>
       <c r="C62">
-        <v>3.018385167485774</v>
+        <v>-1.818361402126243</v>
       </c>
     </row>
     <row r="63">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>-0.1106136132363566</v>
+        <v>0.5021206536948365</v>
       </c>
       <c r="C63">
-        <v>-0.02278379242174616</v>
+        <v>0.2520907787298091</v>
       </c>
     </row>
     <row r="64">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>0.03083386280297059</v>
+        <v>-0.008615966252821534</v>
       </c>
       <c r="C64">
-        <v>0.9038386657359931</v>
+        <v>-0.3969056445154959</v>
       </c>
     </row>
     <row r="65">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>1.839539618117202</v>
+        <v>-1.700114686355838</v>
       </c>
       <c r="C65">
-        <v>0.254821261574298</v>
+        <v>-0.4944073916256887</v>
       </c>
     </row>
     <row r="66">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>-0.4240867575788316</v>
+        <v>1.681472962056194</v>
       </c>
       <c r="C66">
-        <v>1.344420466581619</v>
+        <v>1.386096863889672</v>
       </c>
     </row>
     <row r="67">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>-0.6123508417420929</v>
+        <v>0.02394129977973763</v>
       </c>
       <c r="C67">
-        <v>-1.203399871389254</v>
+        <v>1.413546719233581</v>
       </c>
     </row>
     <row r="68">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>0.1288604123817622</v>
+        <v>-0.3126555864207615</v>
       </c>
       <c r="C68">
-        <v>-0.229762352865635</v>
+        <v>-1.03771553332846</v>
       </c>
     </row>
     <row r="69">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>0.01063364945661098</v>
+        <v>1.857675271355663</v>
       </c>
       <c r="C69">
-        <v>-0.5602342023167002</v>
+        <v>0.1109925615655537</v>
       </c>
     </row>
     <row r="70">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>-0.3400196041777973</v>
+        <v>-0.6282951919311902</v>
       </c>
       <c r="C70">
-        <v>0.2881142085771544</v>
+        <v>1.501318897818816</v>
       </c>
     </row>
     <row r="71">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>0.5203486311736732</v>
+        <v>0.408716365201295</v>
       </c>
       <c r="C71">
-        <v>0.8531501586390612</v>
+        <v>0.4005749986848388</v>
       </c>
     </row>
     <row r="72">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>-1.197336806596876</v>
+        <v>-1.838743877931919</v>
       </c>
       <c r="C72">
-        <v>-1.568283440603632</v>
+        <v>-1.812915979690146</v>
       </c>
     </row>
     <row r="73">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>0.5562241647155574</v>
+        <v>0.9761084918407784</v>
       </c>
       <c r="C73">
-        <v>1.82035345338526</v>
+        <v>1.366972502122495</v>
       </c>
     </row>
     <row r="74">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>1.847762859800356</v>
+        <v>0.6753528289846863</v>
       </c>
       <c r="C74">
-        <v>1.910215296619966</v>
+        <v>0.6504490274810204</v>
       </c>
     </row>
     <row r="75">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>0.8843525834584492</v>
+        <v>0.7759346993547906</v>
       </c>
       <c r="C75">
-        <v>-0.1489528816947782</v>
+        <v>-0.5255244663191825</v>
       </c>
     </row>
     <row r="76">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>-0.2795189291332411</v>
+        <v>0.1398618383662225</v>
       </c>
       <c r="C76">
-        <v>-0.1072631251941291</v>
+        <v>0.01915364776907511</v>
       </c>
     </row>
     <row r="77">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>-2.742649462141791</v>
+        <v>0.8271087943964366</v>
       </c>
       <c r="C77">
-        <v>-0.6868801319467078</v>
+        <v>1.498801951167422</v>
       </c>
     </row>
     <row r="78">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>-1.233254636225348</v>
+        <v>-0.04210948553188886</v>
       </c>
       <c r="C78">
-        <v>-1.468738046317043</v>
+        <v>-1.171282409904655</v>
       </c>
     </row>
     <row r="79">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>2.478332681026998</v>
+        <v>-0.2875127969664004</v>
       </c>
       <c r="C79">
-        <v>1.228804974902808</v>
+        <v>-0.4953650300934063</v>
       </c>
     </row>
     <row r="80">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>0.01588336273472994</v>
+        <v>-0.3601564434790857</v>
       </c>
       <c r="C80">
-        <v>-0.9691358610830338</v>
+        <v>-0.1010034438429241</v>
       </c>
     </row>
     <row r="81">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>-1.31657210657216</v>
+        <v>-0.9653810594264518</v>
       </c>
       <c r="C81">
-        <v>-0.7141811888435354</v>
+        <v>0.4012666906746338</v>
       </c>
     </row>
     <row r="82">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>-0.4517299846907107</v>
+        <v>-0.020286735806495</v>
       </c>
       <c r="C82">
-        <v>-1.123733753306092</v>
+        <v>1.145744997501284</v>
       </c>
     </row>
     <row r="83">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>0.6122577212561316</v>
+        <v>-0.5087195638002916</v>
       </c>
       <c r="C83">
-        <v>0.4183263892494302</v>
+        <v>-0.2959884452632661</v>
       </c>
     </row>
     <row r="84">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>-0.3149444857797171</v>
+        <v>1.08129295603458</v>
       </c>
       <c r="C84">
-        <v>-1.337122859074062</v>
+        <v>0.8421141713268867</v>
       </c>
     </row>
     <row r="85">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>0.8219389147420526</v>
+        <v>0.9922284537323069</v>
       </c>
       <c r="C85">
-        <v>1.46419907613014</v>
+        <v>-0.2658444540238001</v>
       </c>
     </row>
     <row r="86">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="B86">
-        <v>-0.06315490603291309</v>
+        <v>1.65849659921797</v>
       </c>
       <c r="C86">
-        <v>-0.1244741408035057</v>
+        <v>1.369636323855075</v>
       </c>
     </row>
     <row r="87">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B87">
-        <v>1.49151888823074</v>
+        <v>-0.01115180316003376</v>
       </c>
       <c r="C87">
-        <v>1.366188682828562</v>
+        <v>-0.1505792469833482</v>
       </c>
     </row>
     <row r="88">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="B88">
-        <v>1.246946956106819</v>
+        <v>-1.725591332833809</v>
       </c>
       <c r="C88">
-        <v>0.5535613271179689</v>
+        <v>-0.06552215320051147</v>
       </c>
     </row>
     <row r="89">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B89">
-        <v>-0.5160311969689937</v>
+        <v>0.6579691736622577</v>
       </c>
       <c r="C89">
-        <v>-0.9033061825596422</v>
+        <v>0.4723617071895428</v>
       </c>
     </row>
     <row r="90">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="B90">
-        <v>2.536707876974591</v>
+        <v>0.7074005362788802</v>
       </c>
       <c r="C90">
-        <v>0.916321978082253</v>
+        <v>1.288613586930067</v>
       </c>
     </row>
     <row r="91">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="B91">
-        <v>0.7035915573711358</v>
+        <v>0.2540008088218311</v>
       </c>
       <c r="C91">
-        <v>-0.3926136946179655</v>
+        <v>-0.7364722875554307</v>
       </c>
     </row>
     <row r="92">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B92">
-        <v>1.785042599764068</v>
+        <v>1.303516309979818</v>
       </c>
       <c r="C92">
-        <v>-0.385404766019428</v>
+        <v>0.5116430923748245</v>
       </c>
     </row>
     <row r="93">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B93">
-        <v>0.4260852560698151</v>
+        <v>0.9354578073510581</v>
       </c>
       <c r="C93">
-        <v>0.1663784142986474</v>
+        <v>0.8914902945570291</v>
       </c>
     </row>
     <row r="94">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>-0.3232740229692239</v>
+        <v>-0.2140811676362038</v>
       </c>
       <c r="C94">
-        <v>0.05694041038045741</v>
+        <v>-0.2307987221728586</v>
       </c>
     </row>
     <row r="95">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>0.8522709676347232</v>
+        <v>-0.04000861177599295</v>
       </c>
       <c r="C95">
-        <v>2.258881603979578</v>
+        <v>1.785778111482667</v>
       </c>
     </row>
     <row r="96">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="B96">
-        <v>-0.1423787560337434</v>
+        <v>0.02171912673320178</v>
       </c>
       <c r="C96">
-        <v>0.8287651265316448</v>
+        <v>1.082723786487106</v>
       </c>
     </row>
     <row r="97">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="B97">
-        <v>-0.1470012148015583</v>
+        <v>0.1391642302445755</v>
       </c>
       <c r="C97">
-        <v>-0.4363615586258079</v>
+        <v>0.8885833364833876</v>
       </c>
     </row>
     <row r="98">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="B98">
-        <v>-0.3545205122068604</v>
+        <v>1.222558905627694</v>
       </c>
       <c r="C98">
-        <v>0.2280404833164774</v>
+        <v>0.9097028017258103</v>
       </c>
     </row>
     <row r="99">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B99">
-        <v>-1.56836390735805</v>
+        <v>-1.271816573831632</v>
       </c>
       <c r="C99">
-        <v>0.04063575230921301</v>
+        <v>-0.7312490630000154</v>
       </c>
     </row>
     <row r="100">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.1618320313118579</v>
+        <v>-0.09134603932178642</v>
       </c>
       <c r="C100">
-        <v>-0.006610542998191235</v>
+        <v>-1.594552690160353</v>
       </c>
     </row>
     <row r="101">
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="B101">
-        <v>0.4628719089326437</v>
+        <v>-1.28480402794533</v>
       </c>
       <c r="C101">
-        <v>0.7104517457827537</v>
+        <v>-0.3345249185854021</v>
       </c>
     </row>
     <row r="102">
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="B102">
-        <v>-0.9345502848827557</v>
+        <v>0.3308559698041529</v>
       </c>
       <c r="C102">
-        <v>-0.9580642220413328</v>
+        <v>1.277186125056106</v>
       </c>
     </row>
     <row r="103">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="B103">
-        <v>0.3668204530623894</v>
+        <v>0.8825236757996642</v>
       </c>
       <c r="C103">
-        <v>0.3266918712375025</v>
+        <v>-0.8204866070970465</v>
       </c>
     </row>
     <row r="104">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="B104">
-        <v>1.157912854610978</v>
+        <v>0.3360440734097074</v>
       </c>
       <c r="C104">
-        <v>0.5591735564485197</v>
+        <v>-0.6808933177625611</v>
       </c>
     </row>
     <row r="105">
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="B105">
-        <v>0.4695450973189787</v>
+        <v>-0.7292309574638703</v>
       </c>
       <c r="C105">
-        <v>-1.119422783348753</v>
+        <v>-0.8212217247738285</v>
       </c>
     </row>
     <row r="106">
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="B106">
-        <v>-0.5135665679255514</v>
+        <v>1.668610868819324</v>
       </c>
       <c r="C106">
-        <v>-0.8609107241714062</v>
+        <v>1.152211032774404</v>
       </c>
     </row>
     <row r="107">
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="B107">
-        <v>-1.769928415749655</v>
+        <v>-0.5703895169668145</v>
       </c>
       <c r="C107">
-        <v>1.651914639750991</v>
+        <v>1.894882975279493</v>
       </c>
     </row>
     <row r="108">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="B108">
-        <v>-1.817274139607973</v>
+        <v>0.4455676963186162</v>
       </c>
       <c r="C108">
-        <v>-1.134506445264883</v>
+        <v>-0.1016686738273746</v>
       </c>
     </row>
     <row r="109">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="B109">
-        <v>0.734451043542195</v>
+        <v>-0.07777707314372473</v>
       </c>
       <c r="C109">
-        <v>2.232187950742488</v>
+        <v>-0.1445543390381431</v>
       </c>
     </row>
     <row r="110">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B110">
-        <v>-0.1595460802531427</v>
+        <v>-0.4085918262741066</v>
       </c>
       <c r="C110">
-        <v>-0.1429629129344665</v>
+        <v>0.09858292995939799</v>
       </c>
     </row>
     <row r="111">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="B111">
-        <v>-2.495635905457709</v>
+        <v>-1.856465860788843</v>
       </c>
       <c r="C111">
-        <v>-0.4694936048200552</v>
+        <v>-1.045708243378304</v>
       </c>
     </row>
     <row r="112">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="B112">
-        <v>-0.708880804876013</v>
+        <v>-0.1444889084814219</v>
       </c>
       <c r="C112">
-        <v>-0.5954053661319667</v>
+        <v>-0.04888204218778188</v>
       </c>
     </row>
     <row r="113">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="B113">
-        <v>0.7601207287418097</v>
+        <v>0.907565494513119</v>
       </c>
       <c r="C113">
-        <v>0.6733380660160042</v>
+        <v>2.670009732127059</v>
       </c>
     </row>
     <row r="114">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="B114">
-        <v>0.06717401201041928</v>
+        <v>0.03253205962289351</v>
       </c>
       <c r="C114">
-        <v>-0.1853327134439122</v>
+        <v>1.651003255761935</v>
       </c>
     </row>
     <row r="115">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="B115">
-        <v>-0.9966618306985364</v>
+        <v>1.385092645243702</v>
       </c>
       <c r="C115">
-        <v>0.0888680393228059</v>
+        <v>-1.125716478365374</v>
       </c>
     </row>
     <row r="116">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="B116">
-        <v>-0.1304737718630062</v>
+        <v>-0.5137426753100669</v>
       </c>
       <c r="C116">
-        <v>-1.461756071594927</v>
+        <v>0.8417546801902597</v>
       </c>
     </row>
     <row r="117">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="B117">
-        <v>-1.378992788711255</v>
+        <v>0.09875811693152153</v>
       </c>
       <c r="C117">
-        <v>-1.207558841774003</v>
+        <v>0.4953591648568413</v>
       </c>
     </row>
     <row r="118">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="B118">
-        <v>-0.5241106131028684</v>
+        <v>-1.211138349840081</v>
       </c>
       <c r="C118">
-        <v>1.487810431841888</v>
+        <v>-1.463627902392968</v>
       </c>
     </row>
     <row r="119">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="B119">
-        <v>1.592830299272719</v>
+        <v>1.468754987193438</v>
       </c>
       <c r="C119">
-        <v>0.1863634563490042</v>
+        <v>-0.3493060500356652</v>
       </c>
     </row>
     <row r="120">
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="B120">
-        <v>-0.9519202358473179</v>
+        <v>-0.4876282311764636</v>
       </c>
       <c r="C120">
-        <v>-0.08240234350344056</v>
+        <v>-1.426468197572985</v>
       </c>
     </row>
     <row r="121">
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="B121">
-        <v>-0.3282922396488567</v>
+        <v>1.546618334284927</v>
       </c>
       <c r="C121">
-        <v>-0.8705413996257185</v>
+        <v>-0.160035114006271</v>
       </c>
     </row>
     <row r="122">
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="B122">
-        <v>-0.4333329718018795</v>
+        <v>-0.2087845973340217</v>
       </c>
       <c r="C122">
-        <v>-0.4417021135776819</v>
+        <v>-0.9412968185747139</v>
       </c>
     </row>
     <row r="123">
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="B123">
-        <v>0.328301272692108</v>
+        <v>-0.8434344705617889</v>
       </c>
       <c r="C123">
-        <v>0.9496893875308213</v>
+        <v>-0.8327169388154783</v>
       </c>
     </row>
     <row r="124">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="B124">
-        <v>2.283248163115459</v>
+        <v>0.4907913749119942</v>
       </c>
       <c r="C124">
-        <v>1.746715421444399</v>
+        <v>-0.2764166378450603</v>
       </c>
     </row>
     <row r="125">
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="B125">
-        <v>-1.139393317991403</v>
+        <v>-1.225044886796097</v>
       </c>
       <c r="C125">
-        <v>-0.9560372585910489</v>
+        <v>-0.8986885185774807</v>
       </c>
     </row>
     <row r="126">
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="B126">
-        <v>-0.3223840232926095</v>
+        <v>0.4180579054296153</v>
       </c>
       <c r="C126">
-        <v>-0.08991866403531071</v>
+        <v>1.293894515475973</v>
       </c>
     </row>
     <row r="127">
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="B127">
-        <v>0.6183174288587222</v>
+        <v>0.08190628910600313</v>
       </c>
       <c r="C127">
-        <v>-0.5192336304437114</v>
+        <v>0.2497553176100724</v>
       </c>
     </row>
     <row r="128">
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="B128">
-        <v>0.5267369737380507</v>
+        <v>-1.02713713359458</v>
       </c>
       <c r="C128">
-        <v>0.4342827445342304</v>
+        <v>-0.2933740485017146</v>
       </c>
     </row>
     <row r="129">
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="B129">
-        <v>0.09183831641709134</v>
+        <v>-0.3340076314946951</v>
       </c>
       <c r="C129">
-        <v>-0.5722992987484475</v>
+        <v>-1.625610742031229</v>
       </c>
     </row>
     <row r="130">
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="B130">
-        <v>0.256974469220906</v>
+        <v>-1.02240191698829</v>
       </c>
       <c r="C130">
-        <v>-1.391305478084215</v>
+        <v>0.2031777880196582</v>
       </c>
     </row>
     <row r="131">
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="B131">
-        <v>0.9261852698164357</v>
+        <v>0.1484525936070744</v>
       </c>
       <c r="C131">
-        <v>0.894711438284844</v>
+        <v>-0.5396501194748331</v>
       </c>
     </row>
     <row r="132">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="B132">
-        <v>1.650977073592409</v>
+        <v>0.5064291739346727</v>
       </c>
       <c r="C132">
-        <v>1.003953894608773</v>
+        <v>0.8175878333442342</v>
       </c>
     </row>
     <row r="133">
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="B133">
-        <v>-0.8477599442084358</v>
+        <v>-1.632377445292546</v>
       </c>
       <c r="C133">
-        <v>-0.3426325264487606</v>
+        <v>-1.079730300876068</v>
       </c>
     </row>
     <row r="134">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="B134">
-        <v>0.3679901706207577</v>
+        <v>0.4590512062502863</v>
       </c>
       <c r="C134">
-        <v>-0.07857038323251384</v>
+        <v>2.394774214686699</v>
       </c>
     </row>
     <row r="135">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="B135">
-        <v>-0.3533609232525522</v>
+        <v>-0.4877194583548647</v>
       </c>
       <c r="C135">
-        <v>-1.451001668379959</v>
+        <v>-1.614290781699673</v>
       </c>
     </row>
     <row r="136">
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="B136">
-        <v>-0.6533320167828708</v>
+        <v>0.6471619489089149</v>
       </c>
       <c r="C136">
-        <v>-0.3340298989932466</v>
+        <v>-1.051508462086742</v>
       </c>
     </row>
     <row r="137">
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="B137">
-        <v>1.616393900943626</v>
+        <v>1.789762207026029</v>
       </c>
       <c r="C137">
-        <v>-0.07704691761908566</v>
+        <v>-0.04044171551245035</v>
       </c>
     </row>
     <row r="138">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="B138">
-        <v>0.801315446152674</v>
+        <v>0.6779923009898214</v>
       </c>
       <c r="C138">
-        <v>1.874955195577812</v>
+        <v>-0.4280396077960723</v>
       </c>
     </row>
     <row r="139">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="B139">
-        <v>2.074300007412881</v>
+        <v>0.2791365445573158</v>
       </c>
       <c r="C139">
-        <v>2.395076852214761</v>
+        <v>-0.9700870239797013</v>
       </c>
     </row>
     <row r="140">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="B140">
-        <v>0.9996006084800941</v>
+        <v>-0.7348975845429303</v>
       </c>
       <c r="C140">
-        <v>1.15626346239592</v>
+        <v>0.583192124861845</v>
       </c>
     </row>
     <row r="141">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B141">
-        <v>0.2366738197405717</v>
+        <v>-0.04485541294734147</v>
       </c>
       <c r="C141">
-        <v>0.1370591213387565</v>
+        <v>0.2703658857442023</v>
       </c>
     </row>
     <row r="142">
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="B142">
-        <v>0.8322422887730037</v>
+        <v>0.8307509939468748</v>
       </c>
       <c r="C142">
-        <v>-0.9435827481526498</v>
+        <v>0.9085360816772359</v>
       </c>
     </row>
     <row r="143">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="B143">
-        <v>-0.5323923755313181</v>
+        <v>-0.491717817573576</v>
       </c>
       <c r="C143">
-        <v>-0.01830750023797287</v>
+        <v>1.375865288643774</v>
       </c>
     </row>
     <row r="144">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="B144">
-        <v>-0.08378440052422365</v>
+        <v>-2.004201078408453</v>
       </c>
       <c r="C144">
-        <v>-1.694702110643535</v>
+        <v>-1.508066650646606</v>
       </c>
     </row>
     <row r="145">
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="B145">
-        <v>0.2192649779192898</v>
+        <v>0.5799249549645178</v>
       </c>
       <c r="C145">
-        <v>0.261772909297755</v>
+        <v>-0.7079024100438082</v>
       </c>
     </row>
     <row r="146">
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="B146">
-        <v>2.140890522646958</v>
+        <v>0.515583463655829</v>
       </c>
       <c r="C146">
-        <v>1.371565432876844</v>
+        <v>0.1092166547605057</v>
       </c>
     </row>
     <row r="147">
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="B147">
-        <v>1.38212708798227</v>
+        <v>-1.623869508735546</v>
       </c>
       <c r="C147">
-        <v>1.076879194484191</v>
+        <v>-0.6954229430150589</v>
       </c>
     </row>
     <row r="148">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="B148">
-        <v>-0.9826708638731515</v>
+        <v>1.094919508982311</v>
       </c>
       <c r="C148">
-        <v>-0.9952264735689582</v>
+        <v>0.3323931546510474</v>
       </c>
     </row>
     <row r="149">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="B149">
-        <v>2.307409071279122</v>
+        <v>-0.6683848052880449</v>
       </c>
       <c r="C149">
-        <v>0.9170127739272164</v>
+        <v>0.6035343397152717</v>
       </c>
     </row>
     <row r="150">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="B150">
-        <v>-0.7048292454084828</v>
+        <v>0.202609262619791</v>
       </c>
       <c r="C150">
-        <v>-1.523324504567021</v>
+        <v>0.3742105174416909</v>
       </c>
     </row>
     <row r="151">
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="B151">
-        <v>-0.1632257305383005</v>
+        <v>-1.399044802744625</v>
       </c>
       <c r="C151">
-        <v>-0.2179739859733476</v>
+        <v>-0.7252268277580582</v>
       </c>
     </row>
     <row r="152">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="B152">
-        <v>-0.09433309755299704</v>
+        <v>-0.7083434235221815</v>
       </c>
       <c r="C152">
-        <v>0.9394096916842836</v>
+        <v>-1.671791245816076</v>
       </c>
     </row>
     <row r="153">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="B153">
-        <v>0.2722395274687841</v>
+        <v>0.01463277079110682</v>
       </c>
       <c r="C153">
-        <v>0.461282746470787</v>
+        <v>-0.1302094776926346</v>
       </c>
     </row>
     <row r="154">
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="B154">
-        <v>0.2406996289996208</v>
+        <v>0.6103515429248224</v>
       </c>
       <c r="C154">
-        <v>0.6846164875794554</v>
+        <v>0.9607750693202947</v>
       </c>
     </row>
     <row r="155">
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="B155">
-        <v>-0.8035047378309451</v>
+        <v>-1.086597785003775</v>
       </c>
       <c r="C155">
-        <v>0.2428667539024314</v>
+        <v>-1.564555808407428</v>
       </c>
     </row>
     <row r="156">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="B156">
-        <v>-1.252558719194964</v>
+        <v>-1.177271320110757</v>
       </c>
       <c r="C156">
-        <v>-2.063380771054352</v>
+        <v>-1.289641244248325</v>
       </c>
     </row>
     <row r="157">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="B157">
-        <v>-0.3406828336007707</v>
+        <v>0.3121703015682162</v>
       </c>
       <c r="C157">
-        <v>1.248011746201844</v>
+        <v>-1.215335150255989</v>
       </c>
     </row>
     <row r="158">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="B158">
-        <v>-1.60950592382231</v>
+        <v>1.430804260866777</v>
       </c>
       <c r="C158">
-        <v>1.536386421005245</v>
+        <v>1.49813197825635</v>
       </c>
     </row>
     <row r="159">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="B159">
-        <v>1.301575409885297</v>
+        <v>-0.0686533898922885</v>
       </c>
       <c r="C159">
-        <v>1.595991631477445</v>
+        <v>-0.3646253994049025</v>
       </c>
     </row>
     <row r="160">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="B160">
-        <v>-0.414273172968879</v>
+        <v>-1.187204595110176</v>
       </c>
       <c r="C160">
-        <v>-0.2404404544861473</v>
+        <v>-0.2344340677338031</v>
       </c>
     </row>
     <row r="161">
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="B161">
-        <v>-1.464560718500008</v>
+        <v>1.783094009129596</v>
       </c>
       <c r="C161">
-        <v>0.6744549703172266</v>
+        <v>1.136913331212712</v>
       </c>
     </row>
     <row r="162">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="B162">
-        <v>-1.538333491361692</v>
+        <v>-0.7148739696164681</v>
       </c>
       <c r="C162">
-        <v>-1.467246345335711</v>
+        <v>0.2598749568682343</v>
       </c>
     </row>
     <row r="163">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="B163">
-        <v>-0.5973351519214163</v>
+        <v>0.6621993948551723</v>
       </c>
       <c r="C163">
-        <v>-1.212434498252518</v>
+        <v>1.18221289618404</v>
       </c>
     </row>
     <row r="164">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="B164">
-        <v>-0.7512364921969878</v>
+        <v>0.2524702091991653</v>
       </c>
       <c r="C164">
-        <v>-0.5094150367072421</v>
+        <v>0.2595339178011073</v>
       </c>
     </row>
     <row r="165">
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="B165">
-        <v>-0.3797552586160514</v>
+        <v>-0.1745597841972032</v>
       </c>
       <c r="C165">
-        <v>0.8398171435996606</v>
+        <v>0.7874586197113022</v>
       </c>
     </row>
     <row r="166">
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="B166">
-        <v>0.4711258229483716</v>
+        <v>-0.09438697363815966</v>
       </c>
       <c r="C166">
-        <v>0.07229989794293354</v>
+        <v>0.0395496570940571</v>
       </c>
     </row>
     <row r="167">
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="B167">
-        <v>-0.8504545065439296</v>
+        <v>0.09071271449656156</v>
       </c>
       <c r="C167">
-        <v>-0.5363957181947804</v>
+        <v>-1.396928968101844</v>
       </c>
     </row>
     <row r="168">
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="B168">
-        <v>0.9046503126157571</v>
+        <v>-1.637823778083892</v>
       </c>
       <c r="C168">
-        <v>0.4987828093149698</v>
+        <v>0.1781380398610283</v>
       </c>
     </row>
     <row r="169">
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="B169">
-        <v>-1.321931399148121</v>
+        <v>0.6561513141087381</v>
       </c>
       <c r="C169">
-        <v>0.5386049721600983</v>
+        <v>-1.231100428685796</v>
       </c>
     </row>
     <row r="170">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="B170">
-        <v>0.9221527732551026</v>
+        <v>2.56893150685398</v>
       </c>
       <c r="C170">
-        <v>1.178555178973806</v>
+        <v>0.2869052774679522</v>
       </c>
     </row>
     <row r="171">
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="B171">
-        <v>0.374695375613121</v>
+        <v>-0.1108794760033189</v>
       </c>
       <c r="C171">
-        <v>0.2443282028631749</v>
+        <v>0.5790630053177472</v>
       </c>
     </row>
     <row r="172">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B172">
-        <v>1.487625311432084</v>
+        <v>-0.6827354266235641</v>
       </c>
       <c r="C172">
-        <v>0.2006975996311843</v>
+        <v>0.1027130021174718</v>
       </c>
     </row>
     <row r="173">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="B173">
-        <v>2.29159224117844</v>
+        <v>0.1794237615547539</v>
       </c>
       <c r="C173">
-        <v>1.23848359266669</v>
+        <v>-2.643156904518277</v>
       </c>
     </row>
     <row r="174">
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="B174">
-        <v>0.2827866335123167</v>
+        <v>1.578205014497779</v>
       </c>
       <c r="C174">
-        <v>0.4999140296030344</v>
+        <v>1.730905719057179</v>
       </c>
     </row>
     <row r="175">
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="B175">
-        <v>2.505544105789872</v>
+        <v>0.6899195066085235</v>
       </c>
       <c r="C175">
-        <v>0.5360458836322526</v>
+        <v>0.02251784130288231</v>
       </c>
     </row>
     <row r="176">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="B176">
-        <v>-0.5358753999931979</v>
+        <v>-0.7979074283249771</v>
       </c>
       <c r="C176">
-        <v>0.1293224843448259</v>
+        <v>-0.1673910077755199</v>
       </c>
     </row>
     <row r="177">
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="B177">
-        <v>-0.08061023191893561</v>
+        <v>-1.083362586906057</v>
       </c>
       <c r="C177">
-        <v>-1.393259029354968</v>
+        <v>0.3856810654629242</v>
       </c>
     </row>
     <row r="178">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="B178">
-        <v>-1.164895354699123</v>
+        <v>0.7313118442618483</v>
       </c>
       <c r="C178">
-        <v>0.9912964887692284</v>
+        <v>-0.3675568577412772</v>
       </c>
     </row>
     <row r="179">
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="B179">
-        <v>-0.6021802123150326</v>
+        <v>2.131740228893577</v>
       </c>
       <c r="C179">
-        <v>-1.451840147120928</v>
+        <v>1.336089586113682</v>
       </c>
     </row>
     <row r="180">
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="B180">
-        <v>-1.26681783658097</v>
+        <v>0.4037880186953716</v>
       </c>
       <c r="C180">
-        <v>1.13382052525197</v>
+        <v>-0.2337407397725232</v>
       </c>
     </row>
     <row r="181">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="B181">
-        <v>-1.590154737408388</v>
+        <v>-0.2570612107959885</v>
       </c>
       <c r="C181">
-        <v>-0.2406323650746901</v>
+        <v>-0.1682743880655032</v>
       </c>
     </row>
     <row r="182">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="B182">
-        <v>0.5794100950895388</v>
+        <v>-1.116173007968025</v>
       </c>
       <c r="C182">
-        <v>0.5429497593238992</v>
+        <v>-1.154460252060507</v>
       </c>
     </row>
     <row r="183">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="B183">
-        <v>-1.278704145692214</v>
+        <v>-1.015264858882041</v>
       </c>
       <c r="C183">
-        <v>0.6125562338914716</v>
+        <v>-0.639970552211315</v>
       </c>
     </row>
     <row r="184">
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="B184">
-        <v>-0.0280410335562847</v>
+        <v>-0.596335984429339</v>
       </c>
       <c r="C184">
-        <v>-1.667579628892489</v>
+        <v>0.7017031216964142</v>
       </c>
     </row>
     <row r="185">
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="B185">
-        <v>1.30683158844132</v>
+        <v>-0.7203826790687184</v>
       </c>
       <c r="C185">
-        <v>0.4321994964197498</v>
+        <v>-0.1198187460556889</v>
       </c>
     </row>
     <row r="186">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="B186">
-        <v>-0.07482972474436134</v>
+        <v>-0.7289331795921531</v>
       </c>
       <c r="C186">
-        <v>-1.515149406039045</v>
+        <v>-0.7137298649053401</v>
       </c>
     </row>
     <row r="187">
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="B187">
-        <v>0.6765327716346577</v>
+        <v>-2.306800837140685</v>
       </c>
       <c r="C187">
-        <v>-1.541554871232188</v>
+        <v>-0.2431875964425737</v>
       </c>
     </row>
     <row r="188">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="B188">
-        <v>0.8059966698254654</v>
+        <v>-1.154844030952296</v>
       </c>
       <c r="C188">
-        <v>0.3705708940235152</v>
+        <v>0.6179099418475822</v>
       </c>
     </row>
     <row r="189">
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="B189">
-        <v>-0.8579104308056807</v>
+        <v>1.126395819513421</v>
       </c>
       <c r="C189">
-        <v>0.272026347289872</v>
+        <v>1.266354702229859</v>
       </c>
     </row>
     <row r="190">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="B190">
-        <v>-0.3372218795513729</v>
+        <v>1.538184661711433</v>
       </c>
       <c r="C190">
-        <v>-0.909922730924058</v>
+        <v>-0.1826115381663629</v>
       </c>
     </row>
     <row r="191">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="B191">
-        <v>1.538934991258776</v>
+        <v>1.528442929161345</v>
       </c>
       <c r="C191">
-        <v>0.6918421924918499</v>
+        <v>0.3444883177815659</v>
       </c>
     </row>
     <row r="192">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="B192">
-        <v>-0.1087723855710968</v>
+        <v>-2.172725143188067</v>
       </c>
       <c r="C192">
-        <v>-0.5380756264514894</v>
+        <v>-2.000250970820136</v>
       </c>
     </row>
     <row r="193">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="B193">
-        <v>-1.027391864169655</v>
+        <v>0.675062741349401</v>
       </c>
       <c r="C193">
-        <v>0.6422347704448006</v>
+        <v>0.08315454325634161</v>
       </c>
     </row>
     <row r="194">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="B194">
-        <v>-0.2934833986316618</v>
+        <v>-1.032841748405044</v>
       </c>
       <c r="C194">
-        <v>-1.384360848734454</v>
+        <v>1.17538422359528</v>
       </c>
     </row>
     <row r="195">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="B195">
-        <v>0.4479425610284969</v>
+        <v>-0.113138722071751</v>
       </c>
       <c r="C195">
-        <v>0.3662744815287049</v>
+        <v>1.192092699499432</v>
       </c>
     </row>
     <row r="196">
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="B196">
-        <v>1.58846607728641</v>
+        <v>1.04526768512271</v>
       </c>
       <c r="C196">
-        <v>0.809154077797301</v>
+        <v>0.1704088400962965</v>
       </c>
     </row>
     <row r="197">
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="B197">
-        <v>-0.5582145219540542</v>
+        <v>-1.916813995701478</v>
       </c>
       <c r="C197">
-        <v>-1.616723607376392</v>
+        <v>-0.6182742310612949</v>
       </c>
     </row>
     <row r="198">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="B198">
-        <v>-0.9210028740585881</v>
+        <v>-0.04743053725088975</v>
       </c>
       <c r="C198">
-        <v>-0.9937540253869288</v>
+        <v>0.9484356796500389</v>
       </c>
     </row>
     <row r="199">
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="B199">
-        <v>-0.035658283628819</v>
+        <v>0.9508595872311112</v>
       </c>
       <c r="C199">
-        <v>-0.1665501352564041</v>
+        <v>-0.9052158677437588</v>
       </c>
     </row>
     <row r="200">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="B200">
-        <v>0.8429870286204871</v>
+        <v>0.7741692504097557</v>
       </c>
       <c r="C200">
-        <v>1.759718775571218</v>
+        <v>-1.340423772609975</v>
       </c>
     </row>
     <row r="201">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="B201">
-        <v>1.846439435504285</v>
+        <v>-0.728655785529796</v>
       </c>
       <c r="C201">
-        <v>1.128116194505232</v>
+        <v>-1.043828459780427</v>
       </c>
     </row>
   </sheetData>
